--- a/keelinjoyce/rowing/SLU Crew 6k Times.xlsx
+++ b/keelinjoyce/rowing/SLU Crew 6k Times.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/keelinjoyce/Desktop/SYE/github repos/stat450-spr2026-score/keelinjoyce/rowing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00181AA8-4F9C-BF45-AA30-FD7D7A1A814F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DDD2AE2-635B-4F42-B241-A860C3D0E5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12900" yWindow="740" windowWidth="16500" windowHeight="17260" xr2:uid="{78C6AD71-EE53-4441-9D55-D597AB9F7135}"/>
+    <workbookView xWindow="200" yWindow="1440" windowWidth="29200" windowHeight="16560" xr2:uid="{78C6AD71-EE53-4441-9D55-D597AB9F7135}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -113,18 +113,26 @@
     <t>Lucy Fredman</t>
   </si>
   <si>
-    <t>24.25.9</t>
-  </si>
-  <si>
     <t>6k test</t>
+  </si>
+  <si>
+    <t># 6k of season</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -158,13 +166,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="47" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="47" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -479,33 +488,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F853DEF9-F19E-854F-B49D-6F823F8BBB50}">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -527,8 +539,11 @@
       <c r="G2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -550,8 +565,11 @@
       <c r="G3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -573,8 +591,11 @@
       <c r="G4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -596,8 +617,11 @@
       <c r="G5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -619,8 +643,11 @@
       <c r="G6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -642,8 +669,11 @@
       <c r="G7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -665,8 +695,11 @@
       <c r="G8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -688,8 +721,11 @@
       <c r="G9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -711,8 +747,11 @@
       <c r="G10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -734,8 +773,11 @@
       <c r="G11" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -757,8 +799,11 @@
       <c r="G12" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -780,8 +825,11 @@
       <c r="G13" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -803,8 +851,11 @@
       <c r="G14" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
@@ -826,8 +877,11 @@
       <c r="G15" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
@@ -849,8 +903,11 @@
       <c r="G16" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
@@ -872,8 +929,11 @@
       <c r="G17" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>7</v>
       </c>
@@ -895,8 +955,11 @@
       <c r="G18" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>8</v>
       </c>
@@ -918,8 +981,11 @@
       <c r="G19" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -941,8 +1007,11 @@
       <c r="G20" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
@@ -964,8 +1033,11 @@
       <c r="G21" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>13</v>
       </c>
@@ -987,8 +1059,11 @@
       <c r="G22" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>15</v>
       </c>
@@ -1010,8 +1085,11 @@
       <c r="G23" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>9</v>
       </c>
@@ -1033,8 +1111,11 @@
       <c r="G24" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>14</v>
       </c>
@@ -1056,8 +1137,11 @@
       <c r="G25" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>18</v>
       </c>
@@ -1079,8 +1163,11 @@
       <c r="G26" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>11</v>
       </c>
@@ -1102,8 +1189,11 @@
       <c r="G27" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>16</v>
       </c>
@@ -1125,8 +1215,11 @@
       <c r="G28" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>17</v>
       </c>
@@ -1148,8 +1241,11 @@
       <c r="G29" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>20</v>
       </c>
@@ -1171,8 +1267,11 @@
       <c r="G30" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -1194,8 +1293,11 @@
       <c r="G31" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>24</v>
       </c>
@@ -1217,8 +1319,11 @@
       <c r="G32" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>21</v>
       </c>
@@ -1240,8 +1345,11 @@
       <c r="G33" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>22</v>
       </c>
@@ -1263,8 +1371,11 @@
       <c r="G34" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>7</v>
       </c>
@@ -1277,17 +1388,20 @@
       <c r="D35" s="1">
         <v>33</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>25</v>
+      <c r="E35" s="3">
+        <v>1.6966435185185185E-2</v>
       </c>
       <c r="F35" s="5">
         <v>46080</v>
       </c>
       <c r="G35" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="H35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>12</v>
       </c>
@@ -1307,10 +1421,13 @@
         <v>46080</v>
       </c>
       <c r="G36" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="H36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>10</v>
       </c>
@@ -1330,10 +1447,13 @@
         <v>46080</v>
       </c>
       <c r="G37" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="H37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>13</v>
       </c>
@@ -1353,10 +1473,13 @@
         <v>46080</v>
       </c>
       <c r="G38" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="H38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>8</v>
       </c>
@@ -1376,10 +1499,13 @@
         <v>46080</v>
       </c>
       <c r="G39" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="H39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>9</v>
       </c>
@@ -1399,10 +1525,13 @@
         <v>46080</v>
       </c>
       <c r="G40" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="H40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>18</v>
       </c>
@@ -1422,10 +1551,13 @@
         <v>46080</v>
       </c>
       <c r="G41" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="H41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>11</v>
       </c>
@@ -1445,10 +1577,13 @@
         <v>46080</v>
       </c>
       <c r="G42" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="H42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>14</v>
       </c>
@@ -1468,10 +1603,13 @@
         <v>46080</v>
       </c>
       <c r="G43" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="H43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>15</v>
       </c>
@@ -1491,10 +1629,13 @@
         <v>46080</v>
       </c>
       <c r="G44" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="H44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>17</v>
       </c>
@@ -1514,10 +1655,13 @@
         <v>46080</v>
       </c>
       <c r="G45" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="H45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>16</v>
       </c>
@@ -1537,10 +1681,13 @@
         <v>46080</v>
       </c>
       <c r="G46" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="H46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
@@ -1560,10 +1707,13 @@
         <v>46080</v>
       </c>
       <c r="G47" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="H47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>20</v>
       </c>
@@ -1583,10 +1733,13 @@
         <v>46080</v>
       </c>
       <c r="G48" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="H48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>21</v>
       </c>
@@ -1606,10 +1759,13 @@
         <v>46080</v>
       </c>
       <c r="G49" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="H49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>22</v>
       </c>
@@ -1629,7 +1785,10 @@
         <v>46080</v>
       </c>
       <c r="G50" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="H50">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
